--- a/Content/ProjectVD/DataTable/WeaponInfo.xlsx
+++ b/Content/ProjectVD/DataTable/WeaponInfo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thunderfury\ProjectVD\Content\ProjectVD\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A07B1B4C-90F0-44D7-B5D4-4E03DF620DD2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90061E59-C7FB-4DF0-A244-255D2D23F968}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -48,6 +48,10 @@
   </si>
   <si>
     <t>WeaponVisualActorClass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TwoHandSword</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -373,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
@@ -405,6 +409,20 @@
       </c>
       <c r="D2">
         <v>0.2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>20</v>
+      </c>
+      <c r="C3">
+        <v>0.75</v>
+      </c>
+      <c r="D3">
+        <v>0.75</v>
       </c>
     </row>
   </sheetData>
